--- a/evaluation/minimax_sample/confusion_matrices.xlsx
+++ b/evaluation/minimax_sample/confusion_matrices.xlsx
@@ -495,7 +495,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
@@ -607,7 +607,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
@@ -2161,7 +2161,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2228,7 +2228,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -2247,7 +2247,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
@@ -2322,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
